--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>76.5575191894594</v>
+        <v>12.44059686828715</v>
       </c>
       <c r="D2" t="n">
-        <v>80.67544464001176</v>
+        <v>13.10975975400191</v>
       </c>
       <c r="E2" t="n">
-        <v>16.17048589063983</v>
+        <v>2.627703957228974</v>
       </c>
       <c r="F2" t="n">
-        <v>17.39155044302644</v>
+        <v>2.826126946991797</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.09700865229699</v>
+        <v>8.140763905998261</v>
       </c>
       <c r="D3" t="n">
-        <v>49.99818540171824</v>
+        <v>8.124705127779213</v>
       </c>
       <c r="E3" t="n">
-        <v>16.17048589063983</v>
+        <v>2.627703957228974</v>
       </c>
       <c r="F3" t="n">
-        <v>17.39155044302644</v>
+        <v>2.826126946991797</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>57.11356320157174</v>
+        <v>9.280954020255407</v>
       </c>
       <c r="D4" t="n">
-        <v>56.94925338852166</v>
+        <v>9.25425367563477</v>
       </c>
       <c r="E4" t="n">
-        <v>16.17048589063983</v>
+        <v>2.627703957228974</v>
       </c>
       <c r="F4" t="n">
-        <v>17.39155044302644</v>
+        <v>2.826126946991797</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.02548497768873</v>
+        <v>4.229141308874419</v>
       </c>
       <c r="D5" t="n">
-        <v>26.120047536193</v>
+        <v>4.244507724631363</v>
       </c>
       <c r="E5" t="n">
-        <v>16.17048589063983</v>
+        <v>2.627703957228974</v>
       </c>
       <c r="F5" t="n">
-        <v>17.39155044302644</v>
+        <v>2.826126946991797</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>53.39060839292057</v>
+        <v>8.675973863849594</v>
       </c>
       <c r="D6" t="n">
-        <v>53.59389587743537</v>
+        <v>8.709008080083247</v>
       </c>
       <c r="E6" t="n">
-        <v>16.17048589063983</v>
+        <v>2.627703957228974</v>
       </c>
       <c r="F6" t="n">
-        <v>17.39155044302644</v>
+        <v>2.826126946991797</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
